--- a/analysis/혼잡도_분석결과.xlsx
+++ b/analysis/혼잡도_분석결과.xlsx
@@ -445,10 +445,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4075</v>
+        <v>5922</v>
       </c>
       <c r="C2" t="n">
-        <v>3.69</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="3">
@@ -458,10 +458,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3986</v>
+        <v>6146</v>
       </c>
       <c r="C3" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="4">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9234</v>
+        <v>13138</v>
       </c>
       <c r="C4" t="n">
-        <v>8.369999999999999</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="5">
@@ -484,10 +484,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12292</v>
+        <v>18555</v>
       </c>
       <c r="C5" t="n">
-        <v>11.14</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="6">
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7390</v>
+        <v>10886</v>
       </c>
       <c r="C6" t="n">
-        <v>6.7</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="7">
@@ -510,10 +510,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3972</v>
+        <v>6205</v>
       </c>
       <c r="C7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="8">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3986</v>
+        <v>6059</v>
       </c>
       <c r="C8" t="n">
-        <v>3.61</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="9">
@@ -536,10 +536,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4788</v>
+        <v>7348</v>
       </c>
       <c r="C9" t="n">
-        <v>4.34</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="10">
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4528</v>
+        <v>6835</v>
       </c>
       <c r="C10" t="n">
-        <v>4.1</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="11">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4059</v>
+        <v>5902</v>
       </c>
       <c r="C11" t="n">
-        <v>3.68</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="12">
@@ -575,10 +575,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4079</v>
+        <v>6145</v>
       </c>
       <c r="C12" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="13">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3979</v>
+        <v>6090</v>
       </c>
       <c r="C13" t="n">
-        <v>3.61</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="14">
@@ -601,10 +601,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8134</v>
+        <v>12715</v>
       </c>
       <c r="C14" t="n">
-        <v>7.37</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="15">
@@ -614,10 +614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11505</v>
+        <v>17552</v>
       </c>
       <c r="C15" t="n">
-        <v>10.42</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="16">
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8374</v>
+        <v>12235</v>
       </c>
       <c r="C16" t="n">
-        <v>7.59</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="17">
@@ -640,10 +640,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3998</v>
+        <v>6091</v>
       </c>
       <c r="C17" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="18">
@@ -653,10 +653,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4043</v>
+        <v>5815</v>
       </c>
       <c r="C18" t="n">
-        <v>3.66</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="19">
@@ -666,10 +666,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3959</v>
+        <v>6016</v>
       </c>
       <c r="C19" t="n">
-        <v>3.59</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="20">
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3980</v>
+        <v>5869</v>
       </c>
       <c r="C20" t="n">
-        <v>3.61</v>
+        <v>3.55</v>
       </c>
     </row>
   </sheetData>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>359</v>
+        <v>500</v>
       </c>
       <c r="C2" t="n">
-        <v>671.4</v>
+        <v>984.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="3">
@@ -744,13 +744,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>360</v>
+        <v>537</v>
       </c>
       <c r="C3" t="n">
-        <v>653.2</v>
+        <v>1014.4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="4">
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>770.5</v>
+        <v>1214</v>
       </c>
       <c r="C4" t="n">
-        <v>1538.6</v>
+        <v>2142</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="5">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1098.5</v>
+        <v>1537</v>
       </c>
       <c r="C5" t="n">
-        <v>2019</v>
+        <v>3096.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="6">
@@ -792,13 +792,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>654</v>
+        <v>941</v>
       </c>
       <c r="C6" t="n">
-        <v>1216.4</v>
+        <v>1800.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="7">
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>320.5</v>
+        <v>543</v>
       </c>
       <c r="C7" t="n">
-        <v>666.2</v>
+        <v>1023.8</v>
       </c>
       <c r="D7" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="8">
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>326</v>
+        <v>546.5</v>
       </c>
       <c r="C8" t="n">
-        <v>666.8</v>
+        <v>993.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="9">
@@ -840,13 +840,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>411.5</v>
+        <v>645</v>
       </c>
       <c r="C9" t="n">
-        <v>793</v>
+        <v>1211.6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="10">
@@ -856,13 +856,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>377.5</v>
+        <v>582</v>
       </c>
       <c r="C10" t="n">
-        <v>754.6</v>
+        <v>1134.2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="11">
@@ -872,13 +872,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>331.5</v>
+        <v>522</v>
       </c>
       <c r="C11" t="n">
-        <v>679.2</v>
+        <v>971.6</v>
       </c>
       <c r="D11" t="n">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="12">
@@ -888,13 +888,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>348</v>
+        <v>527</v>
       </c>
       <c r="C12" t="n">
-        <v>676.6</v>
+        <v>1018.2</v>
       </c>
       <c r="D12" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="13">
@@ -904,13 +904,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>319.5</v>
+        <v>553.5</v>
       </c>
       <c r="C13" t="n">
-        <v>668</v>
+        <v>996.6</v>
       </c>
       <c r="D13" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>660.5</v>
+        <v>1056.5</v>
       </c>
       <c r="C14" t="n">
-        <v>1362.6</v>
+        <v>2120.4</v>
       </c>
       <c r="D14" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="15">
@@ -936,13 +936,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>996</v>
+        <v>1531.5</v>
       </c>
       <c r="C15" t="n">
-        <v>1902.6</v>
+        <v>2897.8</v>
       </c>
       <c r="D15" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="16">
@@ -952,13 +952,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>733.5</v>
+        <v>1138</v>
       </c>
       <c r="C16" t="n">
-        <v>1381.4</v>
+        <v>1991.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="17">
@@ -968,13 +968,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>346</v>
+        <v>559</v>
       </c>
       <c r="C17" t="n">
-        <v>661.2</v>
+        <v>994.6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="18">
@@ -984,13 +984,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>340.5</v>
+        <v>530</v>
       </c>
       <c r="C18" t="n">
-        <v>672.4</v>
+        <v>951</v>
       </c>
       <c r="D18" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="19">
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>367</v>
+        <v>513.5</v>
       </c>
       <c r="C19" t="n">
-        <v>645</v>
+        <v>997.8</v>
       </c>
       <c r="D19" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="20">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>322</v>
+        <v>502</v>
       </c>
       <c r="C20" t="n">
-        <v>667.2</v>
+        <v>973</v>
       </c>
       <c r="D20" t="n">
-        <v>2.07</v>
+        <v>1.94</v>
       </c>
     </row>
   </sheetData>
@@ -1067,16 +1067,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S1008</t>
+          <t>S1003</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>장위동</t>
+          <t>종로3가</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7439</v>
+        <v>21299</v>
       </c>
     </row>
     <row r="3">
@@ -1085,16 +1085,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S1003</t>
+          <t>S1018</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>종로3가</t>
+          <t>잠실역</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6296</v>
+        <v>17896</v>
       </c>
     </row>
     <row r="4">
@@ -1103,16 +1103,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S1017</t>
+          <t>S1023</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>삼성역</t>
+          <t>공덕역</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6114</v>
+        <v>10937</v>
       </c>
     </row>
     <row r="5">
@@ -1121,16 +1121,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S1020</t>
+          <t>S1026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>신촌</t>
+          <t>신도림</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6072</v>
+        <v>8358</v>
       </c>
     </row>
     <row r="6">
@@ -1139,16 +1139,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S1002</t>
+          <t>S1017</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>광화문</t>
+          <t>삼성역</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5807</v>
+        <v>8194</v>
       </c>
     </row>
     <row r="7">
@@ -1157,16 +1157,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S1010</t>
+          <t>S1012</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>노원역</t>
+          <t>수락산역</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5513</v>
+        <v>7919</v>
       </c>
     </row>
     <row r="8">
@@ -1175,16 +1175,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S1004</t>
+          <t>S1025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>동대문</t>
+          <t>영등포</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4398</v>
+        <v>7731</v>
       </c>
     </row>
     <row r="9">
@@ -1193,16 +1193,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S1028</t>
+          <t>S1007</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>가산디지털단지</t>
+          <t>이문동</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4104</v>
+        <v>7627</v>
       </c>
     </row>
     <row r="10">
@@ -1211,16 +1211,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S1029</t>
+          <t>S1002</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>금천구청</t>
+          <t>광화문</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4068</v>
+        <v>6259</v>
       </c>
     </row>
     <row r="11">
@@ -1229,16 +1229,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S1015</t>
+          <t>S1008</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>역삼역</t>
+          <t>장위동</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3944</v>
+        <v>6024</v>
       </c>
     </row>
   </sheetData>
@@ -1300,17 +1300,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00~18:59</t>
+          <t>08:00~08:59</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1596</v>
+        <v>2472</v>
       </c>
       <c r="E2" t="n">
-        <v>14178</v>
+        <v>21789</v>
       </c>
       <c r="F2" t="n">
-        <v>11.26</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="3">
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2024</v>
+        <v>2987</v>
       </c>
       <c r="E3" t="n">
-        <v>16797</v>
+        <v>23776</v>
       </c>
       <c r="F3" t="n">
-        <v>12.05</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="4">
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:00~08:59</t>
+          <t>18:00~18:59</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1487</v>
+        <v>2181</v>
       </c>
       <c r="E4" t="n">
-        <v>12420</v>
+        <v>19048</v>
       </c>
       <c r="F4" t="n">
-        <v>11.97</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="5">
@@ -1382,13 +1382,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1995</v>
+        <v>3107</v>
       </c>
       <c r="E5" t="n">
-        <v>18132</v>
+        <v>28211</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="6">
@@ -1408,13 +1408,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1148</v>
+        <v>1929</v>
       </c>
       <c r="E6" t="n">
-        <v>10799</v>
+        <v>16130</v>
       </c>
       <c r="F6" t="n">
-        <v>10.63</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="7">
@@ -1430,17 +1430,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>08:00~08:59</t>
+          <t>18:00~18:59</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1396</v>
+        <v>2434</v>
       </c>
       <c r="E7" t="n">
-        <v>13165</v>
+        <v>21033</v>
       </c>
       <c r="F7" t="n">
-        <v>10.6</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="8">
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1742</v>
+        <v>2200</v>
       </c>
       <c r="E8" t="n">
-        <v>15665</v>
+        <v>19957</v>
       </c>
       <c r="F8" t="n">
-        <v>11.12</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="9">
@@ -1482,17 +1482,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>08:00~08:59</t>
+          <t>18:00~18:59</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>950</v>
+        <v>1746</v>
       </c>
       <c r="E9" t="n">
-        <v>9205</v>
+        <v>15580</v>
       </c>
       <c r="F9" t="n">
-        <v>10.32</v>
+        <v>11.21</v>
       </c>
     </row>
   </sheetData>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1603,11 +1603,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>178</v>
+        <v>433</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>242</v>
+        <v>378</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>379</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1678,11 +1678,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>73</v>
+        <v>183</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -1703,11 +1703,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>106</v>
+        <v>192</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -1728,11 +1728,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -1753,11 +1753,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -1778,11 +1778,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>87</v>
+        <v>137</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1828,11 +1828,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>164</v>
+        <v>310</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>312</v>
+        <v>556</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>234</v>
+        <v>338</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1928,11 +1928,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>94</v>
+        <v>182</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1978,11 +1978,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -2003,11 +2003,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2078,11 +2078,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -2103,11 +2103,11 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>348</v>
+        <v>274</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2153,11 +2153,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2228,11 +2228,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>243</v>
+        <v>183</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>260</v>
+        <v>354</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2378,11 +2378,11 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2478,11 +2478,11 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>138</v>
+        <v>95</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>475</v>
+        <v>561</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>612</v>
+        <v>707</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2678,11 +2678,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>216</v>
+        <v>295</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>245</v>
+        <v>203</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>626</v>
+        <v>587</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>424</v>
+        <v>467</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>196</v>
+        <v>246</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2978,11 +2978,11 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>228</v>
+        <v>744</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3003,11 +3003,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>238</v>
+        <v>791</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>515</v>
+        <v>1741</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>674</v>
+        <v>2321</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>425</v>
+        <v>1422</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3103,11 +3103,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>231</v>
+        <v>877</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3128,11 +3128,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>235</v>
+        <v>786</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3153,11 +3153,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>249</v>
+        <v>1049</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>280</v>
+        <v>768</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3203,11 +3203,11 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>204</v>
+        <v>732</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3228,11 +3228,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>219</v>
+        <v>844</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3253,11 +3253,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>229</v>
+        <v>633</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>498</v>
+        <v>1685</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>613</v>
+        <v>2341</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>511</v>
+        <v>1643</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3353,11 +3353,11 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>235</v>
+        <v>684</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3378,11 +3378,11 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>255</v>
+        <v>685</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3403,11 +3403,11 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>208</v>
+        <v>732</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3428,11 +3428,11 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>249</v>
+        <v>821</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -3453,11 +3453,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -3478,7 +3478,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3503,11 +3503,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>548</v>
+        <v>447</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>155</v>
+        <v>190</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>164</v>
+        <v>193</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3703,11 +3703,11 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>196</v>
+        <v>146</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3753,11 +3753,11 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3778,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3803,11 +3803,11 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3978,11 +3978,11 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>277</v>
+        <v>201</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -4003,11 +4003,11 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>333</v>
+        <v>256</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -4028,11 +4028,11 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>255</v>
+        <v>158</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -4053,7 +4053,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4103,11 +4103,11 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>145</v>
+        <v>111</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4253,11 +4253,11 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4378,11 +4378,11 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>80</v>
+        <v>127</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>165</v>
+        <v>281</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>258</v>
+        <v>394</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>153</v>
+        <v>231</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4703,11 +4703,11 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>109</v>
+        <v>245</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>215</v>
+        <v>337</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>93</v>
+        <v>108</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4878,11 +4878,11 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -4903,11 +4903,11 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>100</v>
+        <v>308</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>271</v>
+        <v>563</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>348</v>
+        <v>965</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4978,11 +4978,11 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>231</v>
+        <v>536</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -5003,11 +5003,11 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5028,11 +5028,11 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>117</v>
+        <v>276</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5053,11 +5053,11 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>126</v>
+        <v>363</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>133</v>
+        <v>298</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5103,11 +5103,11 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>124</v>
+        <v>272</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5128,11 +5128,11 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>130</v>
+        <v>241</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5153,11 +5153,11 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>108</v>
+        <v>333</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5178,11 +5178,11 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>241</v>
+        <v>570</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>356</v>
+        <v>784</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>266</v>
+        <v>485</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5253,11 +5253,11 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>119</v>
+        <v>273</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5278,11 +5278,11 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>125</v>
+        <v>256</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5303,11 +5303,11 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>122</v>
+        <v>273</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5328,11 +5328,11 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>125</v>
+        <v>286</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5353,11 +5353,11 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>307</v>
+        <v>249</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>606</v>
+        <v>437</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>929</v>
+        <v>620</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5453,11 +5453,11 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>458</v>
+        <v>360</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5478,7 +5478,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5528,11 +5528,11 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>306</v>
+        <v>267</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5553,11 +5553,11 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>329</v>
+        <v>232</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>264</v>
+        <v>189</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>778</v>
+        <v>668</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>580</v>
+        <v>510</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5778,11 +5778,11 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>314</v>
+        <v>221</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5803,11 +5803,11 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>288</v>
+        <v>201</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>200</v>
+        <v>280</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -5903,11 +5903,11 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>321</v>
+        <v>258</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -5928,11 +5928,11 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>206</v>
+        <v>160</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -5953,7 +5953,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>244</v>
+        <v>180</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6153,11 +6153,11 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>278</v>
+        <v>357</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -6178,11 +6178,11 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6253,7 +6253,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6278,7 +6278,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6353,11 +6353,11 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>408</v>
+        <v>324</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>612</v>
+        <v>726</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6403,11 +6403,11 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>383</v>
+        <v>344</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>223</v>
+        <v>193</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6553,11 +6553,11 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>363</v>
+        <v>451</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6653,7 +6653,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -6753,11 +6753,11 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -6778,11 +6778,11 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>83</v>
+        <v>237</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -6803,11 +6803,11 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>100</v>
+        <v>216</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -6828,11 +6828,11 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>250</v>
+        <v>473</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>289</v>
+        <v>628</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>190</v>
+        <v>377</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -6903,11 +6903,11 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -6928,11 +6928,11 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>143</v>
+        <v>259</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -6978,11 +6978,11 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7003,7 +7003,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7028,11 +7028,11 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7053,11 +7053,11 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7078,11 +7078,11 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>238</v>
+        <v>430</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -7103,11 +7103,11 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>186</v>
+        <v>486</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>202</v>
+        <v>338</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7153,11 +7153,11 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>88</v>
+        <v>241</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7178,11 +7178,11 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>115</v>
+        <v>231</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7203,11 +7203,11 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>125</v>
+        <v>208</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7228,11 +7228,11 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>159</v>
+        <v>243</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7278,11 +7278,11 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>109</v>
+        <v>275</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>317</v>
+        <v>528</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>446</v>
+        <v>1005</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>270</v>
+        <v>477</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>133</v>
+        <v>315</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>131</v>
+        <v>271</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>146</v>
+        <v>338</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>170</v>
+        <v>330</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>141</v>
+        <v>281</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>166</v>
+        <v>298</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>152</v>
+        <v>330</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>271</v>
+        <v>651</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>383</v>
+        <v>876</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -7603,11 +7603,11 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>226</v>
+        <v>581</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>131</v>
+        <v>277</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -7653,7 +7653,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>155</v>
+        <v>258</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>142</v>
+        <v>312</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>161</v>
+        <v>273</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -7753,7 +7753,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -7778,11 +7778,11 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>283</v>
+        <v>183</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7803,11 +7803,11 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -7903,11 +7903,11 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -7928,11 +7928,11 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8053,11 +8053,11 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8078,11 +8078,11 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>204</v>
+        <v>139</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8128,7 +8128,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>71</v>
+        <v>162</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -8253,11 +8253,11 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>125</v>
+        <v>300</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8278,11 +8278,11 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>216</v>
+        <v>480</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -8303,11 +8303,11 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8328,11 +8328,11 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>53</v>
+        <v>178</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -8378,11 +8378,11 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8403,11 +8403,11 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>70</v>
+        <v>205</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8428,11 +8428,11 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>49</v>
+        <v>199</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8453,11 +8453,11 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>70</v>
+        <v>204</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8478,11 +8478,11 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>166</v>
+        <v>394</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -8528,11 +8528,11 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>192</v>
+        <v>550</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>153</v>
+        <v>261</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>60</v>
+        <v>145</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -8653,11 +8653,11 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>56</v>
+        <v>171</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -8703,11 +8703,11 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>171</v>
+        <v>57</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8728,11 +8728,11 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>351</v>
+        <v>133</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8753,11 +8753,11 @@
         </is>
       </c>
       <c r="D290" t="n">
-        <v>476</v>
+        <v>194</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -8778,11 +8778,11 @@
         </is>
       </c>
       <c r="D291" t="n">
-        <v>274</v>
+        <v>84</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="D292" t="n">
-        <v>130</v>
+        <v>54</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -8828,11 +8828,11 @@
         </is>
       </c>
       <c r="D293" t="n">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8853,11 +8853,11 @@
         </is>
       </c>
       <c r="D294" t="n">
-        <v>163</v>
+        <v>53</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8878,11 +8878,11 @@
         </is>
       </c>
       <c r="D295" t="n">
-        <v>171</v>
+        <v>56</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8903,11 +8903,11 @@
         </is>
       </c>
       <c r="D296" t="n">
-        <v>132</v>
+        <v>45</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8928,11 +8928,11 @@
         </is>
       </c>
       <c r="D297" t="n">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
         </is>
       </c>
       <c r="D298" t="n">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -8978,11 +8978,11 @@
         </is>
       </c>
       <c r="D299" t="n">
-        <v>273</v>
+        <v>70</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9003,11 +9003,11 @@
         </is>
       </c>
       <c r="D300" t="n">
-        <v>485</v>
+        <v>183</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -9028,11 +9028,11 @@
         </is>
       </c>
       <c r="D301" t="n">
-        <v>278</v>
+        <v>95</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9053,7 +9053,7 @@
         </is>
       </c>
       <c r="D302" t="n">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -9078,11 +9078,11 @@
         </is>
       </c>
       <c r="D303" t="n">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9103,11 +9103,11 @@
         </is>
       </c>
       <c r="D304" t="n">
-        <v>131</v>
+        <v>72</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
         </is>
       </c>
       <c r="D305" t="n">
-        <v>121</v>
+        <v>44</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -9153,11 +9153,11 @@
         </is>
       </c>
       <c r="D306" t="n">
-        <v>175</v>
+        <v>51</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9178,7 +9178,7 @@
         </is>
       </c>
       <c r="D307" t="n">
-        <v>124</v>
+        <v>45</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -9203,11 +9203,11 @@
         </is>
       </c>
       <c r="D308" t="n">
-        <v>404</v>
+        <v>101</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9228,11 +9228,11 @@
         </is>
       </c>
       <c r="D309" t="n">
-        <v>448</v>
+        <v>165</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9253,11 +9253,11 @@
         </is>
       </c>
       <c r="D310" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
         </is>
       </c>
       <c r="D311" t="n">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -9303,11 +9303,11 @@
         </is>
       </c>
       <c r="D312" t="n">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9328,11 +9328,11 @@
         </is>
       </c>
       <c r="D313" t="n">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="D314" t="n">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="D315" t="n">
-        <v>122</v>
+        <v>60</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -9403,11 +9403,11 @@
         </is>
       </c>
       <c r="D316" t="n">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9428,7 @@
         </is>
       </c>
       <c r="D317" t="n">
-        <v>112</v>
+        <v>47</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -9453,11 +9453,11 @@
         </is>
       </c>
       <c r="D318" t="n">
-        <v>287</v>
+        <v>78</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9478,11 +9478,11 @@
         </is>
       </c>
       <c r="D319" t="n">
-        <v>422</v>
+        <v>153</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9503,11 +9503,11 @@
         </is>
       </c>
       <c r="D320" t="n">
-        <v>297</v>
+        <v>97</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9528,11 +9528,11 @@
         </is>
       </c>
       <c r="D321" t="n">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9553,11 +9553,11 @@
         </is>
       </c>
       <c r="D322" t="n">
-        <v>157</v>
+        <v>26</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9578,11 +9578,11 @@
         </is>
       </c>
       <c r="D323" t="n">
-        <v>140</v>
+        <v>53</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9603,11 +9603,11 @@
         </is>
       </c>
       <c r="D324" t="n">
-        <v>149</v>
+        <v>52</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="D325" t="n">
-        <v>225</v>
+        <v>313</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -9653,7 +9653,7 @@
         </is>
       </c>
       <c r="D326" t="n">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -9678,7 +9678,7 @@
         </is>
       </c>
       <c r="D327" t="n">
-        <v>483</v>
+        <v>678</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="D328" t="n">
-        <v>601</v>
+        <v>943</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         </is>
       </c>
       <c r="D329" t="n">
-        <v>417</v>
+        <v>535</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="D330" t="n">
-        <v>224</v>
+        <v>369</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         </is>
       </c>
       <c r="D331" t="n">
-        <v>207</v>
+        <v>371</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -9803,11 +9803,11 @@
         </is>
       </c>
       <c r="D332" t="n">
-        <v>266</v>
+        <v>356</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
         </is>
       </c>
       <c r="D333" t="n">
-        <v>236</v>
+        <v>347</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         </is>
       </c>
       <c r="D334" t="n">
-        <v>260</v>
+        <v>329</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         </is>
       </c>
       <c r="D335" t="n">
-        <v>247</v>
+        <v>287</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -9903,7 +9903,7 @@
         </is>
       </c>
       <c r="D336" t="n">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         </is>
       </c>
       <c r="D337" t="n">
-        <v>436</v>
+        <v>623</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         </is>
       </c>
       <c r="D338" t="n">
-        <v>699</v>
+        <v>847</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         </is>
       </c>
       <c r="D339" t="n">
-        <v>456</v>
+        <v>584</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="D340" t="n">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="D341" t="n">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         </is>
       </c>
       <c r="D342" t="n">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         </is>
       </c>
       <c r="D343" t="n">
-        <v>229</v>
+        <v>324</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -10103,11 +10103,11 @@
         </is>
       </c>
       <c r="D344" t="n">
-        <v>53</v>
+        <v>597</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10128,11 +10128,11 @@
         </is>
       </c>
       <c r="D345" t="n">
-        <v>61</v>
+        <v>694</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10153,11 +10153,11 @@
         </is>
       </c>
       <c r="D346" t="n">
-        <v>196</v>
+        <v>1323</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10178,11 +10178,11 @@
         </is>
       </c>
       <c r="D347" t="n">
-        <v>201</v>
+        <v>2048</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10203,11 +10203,11 @@
         </is>
       </c>
       <c r="D348" t="n">
-        <v>130</v>
+        <v>1213</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10228,11 +10228,11 @@
         </is>
       </c>
       <c r="D349" t="n">
-        <v>85</v>
+        <v>634</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10253,11 +10253,11 @@
         </is>
       </c>
       <c r="D350" t="n">
-        <v>69</v>
+        <v>740</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10278,11 +10278,11 @@
         </is>
       </c>
       <c r="D351" t="n">
-        <v>69</v>
+        <v>734</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10303,11 +10303,11 @@
         </is>
       </c>
       <c r="D352" t="n">
-        <v>70</v>
+        <v>894</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10328,11 +10328,11 @@
         </is>
       </c>
       <c r="D353" t="n">
-        <v>84</v>
+        <v>597</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10353,11 +10353,11 @@
         </is>
       </c>
       <c r="D354" t="n">
-        <v>48</v>
+        <v>652</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10378,11 +10378,11 @@
         </is>
       </c>
       <c r="D355" t="n">
-        <v>88</v>
+        <v>718</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10403,11 +10403,11 @@
         </is>
       </c>
       <c r="D356" t="n">
-        <v>112</v>
+        <v>1413</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10428,11 +10428,11 @@
         </is>
       </c>
       <c r="D357" t="n">
-        <v>158</v>
+        <v>1577</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10453,11 +10453,11 @@
         </is>
       </c>
       <c r="D358" t="n">
-        <v>127</v>
+        <v>1440</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10478,11 +10478,11 @@
         </is>
       </c>
       <c r="D359" t="n">
-        <v>58</v>
+        <v>827</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10503,11 +10503,11 @@
         </is>
       </c>
       <c r="D360" t="n">
-        <v>63</v>
+        <v>629</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10528,11 +10528,11 @@
         </is>
       </c>
       <c r="D361" t="n">
-        <v>57</v>
+        <v>625</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10553,11 +10553,11 @@
         </is>
       </c>
       <c r="D362" t="n">
-        <v>43</v>
+        <v>541</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="D363" t="n">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         </is>
       </c>
       <c r="D364" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         </is>
       </c>
       <c r="D365" t="n">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         </is>
       </c>
       <c r="D366" t="n">
-        <v>160</v>
+        <v>206</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         </is>
       </c>
       <c r="D367" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         </is>
       </c>
       <c r="D368" t="n">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         </is>
       </c>
       <c r="D369" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -10753,7 +10753,7 @@
         </is>
       </c>
       <c r="D370" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         </is>
       </c>
       <c r="D371" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         </is>
       </c>
       <c r="D372" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -10828,7 +10828,7 @@
         </is>
       </c>
       <c r="D373" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="D374" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="D375" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -10903,7 +10903,7 @@
         </is>
       </c>
       <c r="D376" t="n">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         </is>
       </c>
       <c r="D377" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         </is>
       </c>
       <c r="D380" t="n">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         </is>
       </c>
       <c r="D381" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -11053,11 +11053,11 @@
         </is>
       </c>
       <c r="D382" t="n">
-        <v>228</v>
+        <v>42</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11078,11 +11078,11 @@
         </is>
       </c>
       <c r="D383" t="n">
-        <v>237</v>
+        <v>51</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11103,11 +11103,11 @@
         </is>
       </c>
       <c r="D384" t="n">
-        <v>530</v>
+        <v>124</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11128,11 +11128,11 @@
         </is>
       </c>
       <c r="D385" t="n">
-        <v>670</v>
+        <v>135</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11153,11 +11153,11 @@
         </is>
       </c>
       <c r="D386" t="n">
-        <v>415</v>
+        <v>69</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11178,11 +11178,11 @@
         </is>
       </c>
       <c r="D387" t="n">
-        <v>211</v>
+        <v>42</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11203,11 +11203,11 @@
         </is>
       </c>
       <c r="D388" t="n">
-        <v>224</v>
+        <v>25</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11228,11 +11228,11 @@
         </is>
       </c>
       <c r="D389" t="n">
-        <v>260</v>
+        <v>44</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11253,11 +11253,11 @@
         </is>
       </c>
       <c r="D390" t="n">
-        <v>254</v>
+        <v>48</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11278,11 +11278,11 @@
         </is>
       </c>
       <c r="D391" t="n">
-        <v>200</v>
+        <v>51</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11303,11 +11303,11 @@
         </is>
       </c>
       <c r="D392" t="n">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11328,11 +11328,11 @@
         </is>
       </c>
       <c r="D393" t="n">
-        <v>241</v>
+        <v>42</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11353,11 +11353,11 @@
         </is>
       </c>
       <c r="D394" t="n">
-        <v>429</v>
+        <v>79</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11378,11 +11378,11 @@
         </is>
       </c>
       <c r="D395" t="n">
-        <v>621</v>
+        <v>136</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11403,11 +11403,11 @@
         </is>
       </c>
       <c r="D396" t="n">
-        <v>452</v>
+        <v>94</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11428,11 +11428,11 @@
         </is>
       </c>
       <c r="D397" t="n">
-        <v>245</v>
+        <v>30</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11453,11 +11453,11 @@
         </is>
       </c>
       <c r="D398" t="n">
-        <v>207</v>
+        <v>52</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11478,11 +11478,11 @@
         </is>
       </c>
       <c r="D399" t="n">
-        <v>198</v>
+        <v>47</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11503,11 +11503,11 @@
         </is>
       </c>
       <c r="D400" t="n">
-        <v>239</v>
+        <v>35</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="D401" t="n">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -11553,11 +11553,11 @@
         </is>
       </c>
       <c r="D402" t="n">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11578,11 +11578,11 @@
         </is>
       </c>
       <c r="D403" t="n">
-        <v>351</v>
+        <v>76</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11603,11 +11603,11 @@
         </is>
       </c>
       <c r="D404" t="n">
-        <v>446</v>
+        <v>137</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11628,11 +11628,11 @@
         </is>
       </c>
       <c r="D405" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11653,11 +11653,11 @@
         </is>
       </c>
       <c r="D406" t="n">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
         </is>
       </c>
       <c r="D407" t="n">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -11703,11 +11703,11 @@
         </is>
       </c>
       <c r="D408" t="n">
-        <v>181</v>
+        <v>47</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11728,11 +11728,11 @@
         </is>
       </c>
       <c r="D409" t="n">
-        <v>175</v>
+        <v>44</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="D410" t="n">
-        <v>124</v>
+        <v>37</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -11778,11 +11778,11 @@
         </is>
       </c>
       <c r="D411" t="n">
-        <v>148</v>
+        <v>46</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11803,7 +11803,7 @@
         </is>
       </c>
       <c r="D412" t="n">
-        <v>118</v>
+        <v>43</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -11828,11 +11828,11 @@
         </is>
       </c>
       <c r="D413" t="n">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11853,11 +11853,11 @@
         </is>
       </c>
       <c r="D414" t="n">
-        <v>355</v>
+        <v>96</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11878,11 +11878,11 @@
         </is>
       </c>
       <c r="D415" t="n">
-        <v>276</v>
+        <v>74</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11903,11 +11903,11 @@
         </is>
       </c>
       <c r="D416" t="n">
-        <v>144</v>
+        <v>35</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11928,11 +11928,11 @@
         </is>
       </c>
       <c r="D417" t="n">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11953,11 +11953,11 @@
         </is>
       </c>
       <c r="D418" t="n">
-        <v>157</v>
+        <v>43</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
         </is>
       </c>
       <c r="D419" t="n">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         </is>
       </c>
       <c r="D420" t="n">
-        <v>75</v>
+        <v>41</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="D421" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -12053,11 +12053,11 @@
         </is>
       </c>
       <c r="D422" t="n">
-        <v>175</v>
+        <v>74</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -12078,11 +12078,11 @@
         </is>
       </c>
       <c r="D423" t="n">
-        <v>224</v>
+        <v>101</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -12103,11 +12103,11 @@
         </is>
       </c>
       <c r="D424" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
         </is>
       </c>
       <c r="D425" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -12153,7 +12153,7 @@
         </is>
       </c>
       <c r="D426" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         </is>
       </c>
       <c r="D427" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="D428" t="n">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         </is>
       </c>
       <c r="D429" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -12253,7 +12253,7 @@
         </is>
       </c>
       <c r="D430" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="D431" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         </is>
       </c>
       <c r="D432" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -12328,11 +12328,11 @@
         </is>
       </c>
       <c r="D433" t="n">
-        <v>235</v>
+        <v>108</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
         </is>
       </c>
       <c r="D434" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         </is>
       </c>
       <c r="D435" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="D436" t="n">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         </is>
       </c>
       <c r="D437" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -12453,7 +12453,7 @@
         </is>
       </c>
       <c r="D438" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         </is>
       </c>
       <c r="D439" t="n">
-        <v>135</v>
+        <v>394</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -12503,11 +12503,11 @@
         </is>
       </c>
       <c r="D440" t="n">
-        <v>118</v>
+        <v>402</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -12528,11 +12528,11 @@
         </is>
       </c>
       <c r="D441" t="n">
-        <v>240</v>
+        <v>858</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12553,7 +12553,7 @@
         </is>
       </c>
       <c r="D442" t="n">
-        <v>422</v>
+        <v>1260</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -12578,11 +12578,11 @@
         </is>
       </c>
       <c r="D443" t="n">
-        <v>206</v>
+        <v>666</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12603,11 +12603,11 @@
         </is>
       </c>
       <c r="D444" t="n">
-        <v>99</v>
+        <v>405</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12628,11 +12628,11 @@
         </is>
       </c>
       <c r="D445" t="n">
-        <v>117</v>
+        <v>387</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -12653,11 +12653,11 @@
         </is>
       </c>
       <c r="D446" t="n">
-        <v>139</v>
+        <v>536</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12678,11 +12678,11 @@
         </is>
       </c>
       <c r="D447" t="n">
-        <v>147</v>
+        <v>499</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12703,7 @@
         </is>
       </c>
       <c r="D448" t="n">
-        <v>154</v>
+        <v>393</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -12728,11 +12728,11 @@
         </is>
       </c>
       <c r="D449" t="n">
-        <v>120</v>
+        <v>431</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12753,7 +12753,7 @@
         </is>
       </c>
       <c r="D450" t="n">
-        <v>141</v>
+        <v>383</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
@@ -12778,11 +12778,11 @@
         </is>
       </c>
       <c r="D451" t="n">
-        <v>254</v>
+        <v>780</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12803,7 +12803,7 @@
         </is>
       </c>
       <c r="D452" t="n">
-        <v>364</v>
+        <v>1163</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -12828,11 +12828,11 @@
         </is>
       </c>
       <c r="D453" t="n">
-        <v>253</v>
+        <v>730</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12853,11 +12853,11 @@
         </is>
       </c>
       <c r="D454" t="n">
-        <v>120</v>
+        <v>388</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
         </is>
       </c>
       <c r="D455" t="n">
-        <v>142</v>
+        <v>392</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -12903,11 +12903,11 @@
         </is>
       </c>
       <c r="D456" t="n">
-        <v>129</v>
+        <v>457</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12928,11 +12928,11 @@
         </is>
       </c>
       <c r="D457" t="n">
-        <v>123</v>
+        <v>413</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -12953,11 +12953,11 @@
         </is>
       </c>
       <c r="D458" t="n">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -12978,7 +12978,7 @@
         </is>
       </c>
       <c r="D459" t="n">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -13003,11 +13003,11 @@
         </is>
       </c>
       <c r="D460" t="n">
-        <v>268</v>
+        <v>371</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13028,7 +13028,7 @@
         </is>
       </c>
       <c r="D461" t="n">
-        <v>358</v>
+        <v>533</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="D462" t="n">
-        <v>226</v>
+        <v>294</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="D463" t="n">
-        <v>126</v>
+        <v>158</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -13103,7 +13103,7 @@
         </is>
       </c>
       <c r="D464" t="n">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         </is>
       </c>
       <c r="D465" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -13153,11 +13153,11 @@
         </is>
       </c>
       <c r="D466" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -13178,7 +13178,7 @@
         </is>
       </c>
       <c r="D467" t="n">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -13203,11 +13203,11 @@
         </is>
       </c>
       <c r="D468" t="n">
-        <v>115</v>
+        <v>171</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13228,11 +13228,11 @@
         </is>
       </c>
       <c r="D469" t="n">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -13253,7 +13253,7 @@
         </is>
       </c>
       <c r="D470" t="n">
-        <v>255</v>
+        <v>348</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="D471" t="n">
-        <v>391</v>
+        <v>478</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -13303,11 +13303,11 @@
         </is>
       </c>
       <c r="D472" t="n">
-        <v>270</v>
+        <v>354</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13328,7 @@
         </is>
       </c>
       <c r="D473" t="n">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="D474" t="n">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -13378,11 +13378,11 @@
         </is>
       </c>
       <c r="D475" t="n">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="D476" t="n">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -13428,11 +13428,11 @@
         </is>
       </c>
       <c r="D477" t="n">
-        <v>76</v>
+        <v>284</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13453,11 +13453,11 @@
         </is>
       </c>
       <c r="D478" t="n">
-        <v>52</v>
+        <v>283</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13478,11 +13478,11 @@
         </is>
       </c>
       <c r="D479" t="n">
-        <v>121</v>
+        <v>593</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -13503,11 +13503,11 @@
         </is>
       </c>
       <c r="D480" t="n">
-        <v>178</v>
+        <v>792</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -13528,11 +13528,11 @@
         </is>
       </c>
       <c r="D481" t="n">
-        <v>90</v>
+        <v>430</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -13553,11 +13553,11 @@
         </is>
       </c>
       <c r="D482" t="n">
-        <v>62</v>
+        <v>309</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13578,11 +13578,11 @@
         </is>
       </c>
       <c r="D483" t="n">
-        <v>79</v>
+        <v>242</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13603,11 +13603,11 @@
         </is>
       </c>
       <c r="D484" t="n">
-        <v>81</v>
+        <v>295</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13628,11 +13628,11 @@
         </is>
       </c>
       <c r="D485" t="n">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13653,11 +13653,11 @@
         </is>
       </c>
       <c r="D486" t="n">
-        <v>64</v>
+        <v>260</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13678,11 +13678,11 @@
         </is>
       </c>
       <c r="D487" t="n">
-        <v>48</v>
+        <v>338</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13703,11 +13703,11 @@
         </is>
       </c>
       <c r="D488" t="n">
-        <v>67</v>
+        <v>347</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13728,11 +13728,11 @@
         </is>
       </c>
       <c r="D489" t="n">
-        <v>128</v>
+        <v>623</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -13753,11 +13753,11 @@
         </is>
       </c>
       <c r="D490" t="n">
-        <v>170</v>
+        <v>892</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -13778,11 +13778,11 @@
         </is>
       </c>
       <c r="D491" t="n">
-        <v>173</v>
+        <v>624</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -13803,11 +13803,11 @@
         </is>
       </c>
       <c r="D492" t="n">
-        <v>67</v>
+        <v>291</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13828,11 +13828,11 @@
         </is>
       </c>
       <c r="D493" t="n">
-        <v>53</v>
+        <v>278</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13853,11 +13853,11 @@
         </is>
       </c>
       <c r="D494" t="n">
-        <v>54</v>
+        <v>219</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13878,11 +13878,11 @@
         </is>
       </c>
       <c r="D495" t="n">
-        <v>64</v>
+        <v>277</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -13903,7 +13903,7 @@
         </is>
       </c>
       <c r="D496" t="n">
-        <v>147</v>
+        <v>296</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="D497" t="n">
-        <v>149</v>
+        <v>391</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -13953,11 +13953,11 @@
         </is>
       </c>
       <c r="D498" t="n">
-        <v>230</v>
+        <v>768</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -13978,7 +13978,7 @@
         </is>
       </c>
       <c r="D499" t="n">
-        <v>338</v>
+        <v>927</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -14003,11 +14003,11 @@
         </is>
       </c>
       <c r="D500" t="n">
-        <v>264</v>
+        <v>526</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -14028,11 +14028,11 @@
         </is>
       </c>
       <c r="D501" t="n">
-        <v>119</v>
+        <v>288</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="D502" t="n">
-        <v>139</v>
+        <v>272</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="D503" t="n">
-        <v>155</v>
+        <v>311</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         </is>
       </c>
       <c r="D504" t="n">
-        <v>145</v>
+        <v>328</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         </is>
       </c>
       <c r="D505" t="n">
-        <v>131</v>
+        <v>285</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         </is>
       </c>
       <c r="D506" t="n">
-        <v>148</v>
+        <v>297</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         </is>
       </c>
       <c r="D507" t="n">
-        <v>131</v>
+        <v>346</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="D508" t="n">
-        <v>284</v>
+        <v>564</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="D509" t="n">
-        <v>410</v>
+        <v>874</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -14253,7 +14253,7 @@
         </is>
       </c>
       <c r="D510" t="n">
-        <v>269</v>
+        <v>655</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -14278,11 +14278,11 @@
         </is>
       </c>
       <c r="D511" t="n">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14303,11 +14303,11 @@
         </is>
       </c>
       <c r="D512" t="n">
-        <v>124</v>
+        <v>295</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14328,11 +14328,11 @@
         </is>
       </c>
       <c r="D513" t="n">
-        <v>104</v>
+        <v>361</v>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14353,11 +14353,11 @@
         </is>
       </c>
       <c r="D514" t="n">
-        <v>95</v>
+        <v>285</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="D515" t="n">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="E515" t="inlineStr">
         <is>
@@ -14403,11 +14403,11 @@
         </is>
       </c>
       <c r="D516" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -14428,11 +14428,11 @@
         </is>
       </c>
       <c r="D517" t="n">
-        <v>366</v>
+        <v>330</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14453,11 +14453,11 @@
         </is>
       </c>
       <c r="D518" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14478,7 +14478,7 @@
         </is>
       </c>
       <c r="D519" t="n">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         </is>
       </c>
       <c r="D520" t="n">
-        <v>85</v>
+        <v>135</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
@@ -14528,11 +14528,11 @@
         </is>
       </c>
       <c r="D521" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -14553,7 +14553,7 @@
         </is>
       </c>
       <c r="D522" t="n">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
@@ -14578,11 +14578,11 @@
         </is>
       </c>
       <c r="D523" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -14603,11 +14603,11 @@
         </is>
       </c>
       <c r="D524" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -14628,11 +14628,11 @@
         </is>
       </c>
       <c r="D525" t="n">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -14653,7 +14653,7 @@
         </is>
       </c>
       <c r="D526" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
@@ -14678,11 +14678,11 @@
         </is>
       </c>
       <c r="D527" t="n">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14703,7 +14703,7 @@
         </is>
       </c>
       <c r="D528" t="n">
-        <v>363</v>
+        <v>410</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
@@ -14728,11 +14728,11 @@
         </is>
       </c>
       <c r="D529" t="n">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14753,7 +14753,7 @@
         </is>
       </c>
       <c r="D530" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
@@ -14778,11 +14778,11 @@
         </is>
       </c>
       <c r="D531" t="n">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -14803,7 +14803,7 @@
         </is>
       </c>
       <c r="D532" t="n">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
@@ -14828,11 +14828,11 @@
         </is>
       </c>
       <c r="D533" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -14853,7 +14853,7 @@
         </is>
       </c>
       <c r="D534" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
@@ -14878,7 +14878,7 @@
         </is>
       </c>
       <c r="D535" t="n">
-        <v>159</v>
+        <v>202</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
@@ -14903,11 +14903,11 @@
         </is>
       </c>
       <c r="D536" t="n">
-        <v>298</v>
+        <v>387</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="D537" t="n">
-        <v>463</v>
+        <v>574</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         </is>
       </c>
       <c r="D538" t="n">
-        <v>300</v>
+        <v>424</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         </is>
       </c>
       <c r="D539" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="D540" t="n">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         </is>
       </c>
       <c r="D541" t="n">
-        <v>189</v>
+        <v>275</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         </is>
       </c>
       <c r="D542" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -15078,7 +15078,7 @@
         </is>
       </c>
       <c r="D543" t="n">
-        <v>155</v>
+        <v>225</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
@@ -15103,11 +15103,11 @@
         </is>
       </c>
       <c r="D544" t="n">
-        <v>122</v>
+        <v>214</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -15128,7 +15128,7 @@
         </is>
       </c>
       <c r="D545" t="n">
-        <v>145</v>
+        <v>252</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         </is>
       </c>
       <c r="D546" t="n">
-        <v>326</v>
+        <v>482</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="D547" t="n">
-        <v>473</v>
+        <v>542</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
@@ -15203,11 +15203,11 @@
         </is>
       </c>
       <c r="D548" t="n">
-        <v>246</v>
+        <v>409</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>상</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15228,7 @@
         </is>
       </c>
       <c r="D549" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
@@ -15253,11 +15253,11 @@
         </is>
       </c>
       <c r="D550" t="n">
-        <v>122</v>
+        <v>240</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -15278,7 +15278,7 @@
         </is>
       </c>
       <c r="D551" t="n">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="D552" t="n">
-        <v>156</v>
+        <v>215</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -15328,11 +15328,11 @@
         </is>
       </c>
       <c r="D553" t="n">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
         </is>
       </c>
       <c r="D554" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
@@ -15378,11 +15378,11 @@
         </is>
       </c>
       <c r="D555" t="n">
-        <v>346</v>
+        <v>323</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -15403,7 +15403,7 @@
         </is>
       </c>
       <c r="D556" t="n">
-        <v>447</v>
+        <v>419</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
@@ -15428,11 +15428,11 @@
         </is>
       </c>
       <c r="D557" t="n">
-        <v>324</v>
+        <v>224</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -15453,11 +15453,11 @@
         </is>
       </c>
       <c r="D558" t="n">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15478,11 +15478,11 @@
         </is>
       </c>
       <c r="D559" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15503,11 +15503,11 @@
         </is>
       </c>
       <c r="D560" t="n">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15528,11 +15528,11 @@
         </is>
       </c>
       <c r="D561" t="n">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15553,11 +15553,11 @@
         </is>
       </c>
       <c r="D562" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15578,11 +15578,11 @@
         </is>
       </c>
       <c r="D563" t="n">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
         </is>
       </c>
       <c r="D564" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
@@ -15628,11 +15628,11 @@
         </is>
       </c>
       <c r="D565" t="n">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -15653,11 +15653,11 @@
         </is>
       </c>
       <c r="D566" t="n">
-        <v>395</v>
+        <v>368</v>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -15678,11 +15678,11 @@
         </is>
       </c>
       <c r="D567" t="n">
-        <v>305</v>
+        <v>245</v>
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>상</t>
+          <t>중</t>
         </is>
       </c>
     </row>
@@ -15703,11 +15703,11 @@
         </is>
       </c>
       <c r="D568" t="n">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15728,7 +15728,7 @@
         </is>
       </c>
       <c r="D569" t="n">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E569" t="inlineStr">
         <is>
@@ -15753,11 +15753,11 @@
         </is>
       </c>
       <c r="D570" t="n">
-        <v>156</v>
+        <v>110</v>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15778,11 +15778,11 @@
         </is>
       </c>
       <c r="D571" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
     </row>
@@ -15829,7 +15829,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>하차합계 &gt;= 266</t>
+          <t>하차합계 &gt;= 403</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>131 &lt;= 하차합계 &lt; 266</t>
+          <t>166 &lt;= 하차합계 &lt; 403</t>
         </is>
       </c>
     </row>
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>하차합계 &lt; 131</t>
+          <t>하차합계 &lt; 166</t>
         </is>
       </c>
     </row>
